--- a/Einzelabend_15.06.2026.xlsx
+++ b/Einzelabend_15.06.2026.xlsx
@@ -888,6 +888,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Aufstehen</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
         <v>Pünkt</v>
